--- a/astro-site/public/dl/plan-catering-tematico-eventos/checklist-apertura-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/checklist-apertura-catering-tematico-eventos.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Mínimo 600.000 €: lo piden las fincas, los hoteles y las empresas grandes. Pide el certificado para adjuntarlo a los presupuestos</t>
+          <t>Recomendado: al menos 600.000 €; es lo que suelen pedir las fincas, los hoteles y las empresas grandes. Pide el certificado para adjuntarlo a los presupuestos</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Particulares: más de 21 días, se devuelve el anticipo; 21-7 días, se retiene el 50 %; menos de 7 días, el 100 %. Empresas: tramos de 28, 14 y 7 días</t>
+          <t>Particulares: más de 21 días, se devuelve el anticipo; 21-7 días, se retiene el 50 % del anticipo; menos de 7 días, el anticipo entero (y con menos de 48 horas, además, el 50 % del total). Empresas: tramos de 28, 14 y 7 días</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Este fichero forma parte del producto «plan-negocio-food-truck» de AI Chef Pro.</t>
+          <t>Este fichero forma parte del producto «plan-catering-tematico-eventos» de AI Chef Pro.</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-catering-tematico-eventos/checklist-apertura-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/checklist-apertura-catering-tematico-eventos.xlsx
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Cadena de frío y de caliente en producción, transporte y estación: 63 °C o más en caliente, 4-8 °C o menos en frío (art. 30 del RD 1086/2020). Registros de temperatura en cada evento</t>
+          <t>Cadena de frío y de caliente en producción, transporte y estación: 63 °C o más en caliente, 4-8 °C o menos en frío (art. 30 del RD 1086/2020). Registros de temperatura en cada evento. Guarda una comida testigo de cada plato (100 g, identificada y fechada, a 4 °C o menos o congelada, 7 días): obligatoria en eventos y en encargos de más de 40 personas (art. 30.8 y 30.10 del RD 1086/2020)</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Temperaturas registradas en cada estación</t>
+          <t>Temperaturas registradas en cada estación y comida testigo de cada plato (art. 30.8 del RD 1086/2020)</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-catering-tematico-eventos/checklist-apertura-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/checklist-apertura-catering-tematico-eventos.xlsx
@@ -951,8 +951,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1463,8 +1463,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1948,8 +1948,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2325,8 +2325,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2864,8 +2864,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -3376,8 +3376,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
